--- a/outputs/docling_ablation/summary.xlsx
+++ b/outputs/docling_ablation/summary.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="73">
   <si>
     <t>pdf_filename</t>
   </si>
@@ -22,13 +22,70 @@
     <t>profile</t>
   </si>
   <si>
+    <t>profile_group</t>
+  </si>
+  <si>
+    <t>quality_tier</t>
+  </si>
+  <si>
+    <t>resource_class</t>
+  </si>
+  <si>
     <t>status</t>
   </si>
   <si>
+    <t>skip_reason</t>
+  </si>
+  <si>
+    <t>error_message</t>
+  </si>
+  <si>
     <t>runtime_seconds</t>
   </si>
   <si>
-    <t>selected_device</t>
+    <t>pipeline</t>
+  </si>
+  <si>
+    <t>pdf_backend</t>
+  </si>
+  <si>
+    <t>table_mode</t>
+  </si>
+  <si>
+    <t>do_cell_matching</t>
+  </si>
+  <si>
+    <t>ocr_engine</t>
+  </si>
+  <si>
+    <t>ocr_lang</t>
+  </si>
+  <si>
+    <t>psm</t>
+  </si>
+  <si>
+    <t>do_ocr</t>
+  </si>
+  <si>
+    <t>force_full_page_ocr</t>
+  </si>
+  <si>
+    <t>vlm_model</t>
+  </si>
+  <si>
+    <t>images_scale</t>
+  </si>
+  <si>
+    <t>generate_page_images</t>
+  </si>
+  <si>
+    <t>generate_picture_images</t>
+  </si>
+  <si>
+    <t>device_requested</t>
+  </si>
+  <si>
+    <t>device_selected</t>
   </si>
   <si>
     <t>gpu_available</t>
@@ -37,7 +94,19 @@
     <t>gpu_name</t>
   </si>
   <si>
-    <t>number_of_tables</t>
+    <t>gpu_memory_total_mb</t>
+  </si>
+  <si>
+    <t>gpu_memory_before_mb</t>
+  </si>
+  <si>
+    <t>gpu_memory_after_mb</t>
+  </si>
+  <si>
+    <t>page_count</t>
+  </si>
+  <si>
+    <t>table_count</t>
   </si>
   <si>
     <t>markdown_output_path</t>
@@ -46,110 +115,132 @@
     <t>json_output_path</t>
   </si>
   <si>
-    <t>error_or_skip_reason</t>
+    <t>run_dir</t>
   </si>
   <si>
     <t>MANUAL DE MARKETING NASTIZOL MULTISINTOMAS.pdf</t>
   </si>
   <si>
-    <t>standard_fast_no_ocr</t>
-  </si>
-  <si>
     <t>standard_accurate_no_ocr</t>
   </si>
   <si>
-    <t>standard_accurate_cellmatch_false</t>
-  </si>
-  <si>
-    <t>standard_tesseract_ocr_psm3</t>
-  </si>
-  <si>
-    <t>standard_tesseract_force_ocr_psm6</t>
-  </si>
-  <si>
-    <t>standard_easyocr_force_ocr</t>
-  </si>
-  <si>
-    <t>standard_cuda_accurate</t>
-  </si>
-  <si>
-    <t>vlm_granite_docling_cuda</t>
+    <t>standard_accurate_no_ocr_doclingparse_cellmatch_true</t>
+  </si>
+  <si>
+    <t>standard_accurate_no_ocr_doclingparse_cellmatch_false</t>
+  </si>
+  <si>
+    <t>standard_accurate_no_ocr_pypdfium2_cellmatch_true</t>
+  </si>
+  <si>
+    <t>standard_accurate_no_ocr_pypdfium2_cellmatch_false</t>
+  </si>
+  <si>
+    <t>standard_accurate_no_ocr_threaded_doclingparse_cellmatch_true</t>
+  </si>
+  <si>
+    <t>standard_accurate_no_ocr_threaded_doclingparse_cellmatch_false</t>
+  </si>
+  <si>
+    <t>native_text</t>
+  </si>
+  <si>
+    <t>strong</t>
+  </si>
+  <si>
+    <t>high</t>
   </si>
   <si>
     <t>success</t>
   </si>
   <si>
+    <t>standard</t>
+  </si>
+  <si>
+    <t>docling_parse</t>
+  </si>
+  <si>
+    <t>pypdfium2</t>
+  </si>
+  <si>
+    <t>threaded_docling_parse</t>
+  </si>
+  <si>
+    <t>accurate</t>
+  </si>
+  <si>
     <t>auto</t>
   </si>
   <si>
-    <t>cuda</t>
-  </si>
-  <si>
-    <t>Tesla T4</t>
-  </si>
-  <si>
-    <t>/content/ConversionExperiments/outputs/docling_ablation/MANUAL DE MARKETING NASTIZOL MULTISINTOMAS/standard_fast_no_ocr/output.md</t>
-  </si>
-  <si>
-    <t>/content/ConversionExperiments/outputs/docling_ablation/MANUAL DE MARKETING NASTIZOL MULTISINTOMAS/standard_accurate_no_ocr/output.md</t>
-  </si>
-  <si>
-    <t>/content/ConversionExperiments/outputs/docling_ablation/MANUAL DE MARKETING NASTIZOL MULTISINTOMAS/standard_accurate_cellmatch_false/output.md</t>
-  </si>
-  <si>
-    <t>/content/ConversionExperiments/outputs/docling_ablation/MANUAL DE MARKETING NASTIZOL MULTISINTOMAS/standard_tesseract_ocr_psm3/output.md</t>
-  </si>
-  <si>
-    <t>/content/ConversionExperiments/outputs/docling_ablation/MANUAL DE MARKETING NASTIZOL MULTISINTOMAS/standard_tesseract_force_ocr_psm6/output.md</t>
-  </si>
-  <si>
-    <t>/content/ConversionExperiments/outputs/docling_ablation/MANUAL DE MARKETING NASTIZOL MULTISINTOMAS/standard_easyocr_force_ocr/output.md</t>
-  </si>
-  <si>
-    <t>/content/ConversionExperiments/outputs/docling_ablation/MANUAL DE MARKETING NASTIZOL MULTISINTOMAS/standard_cuda_accurate/output.md</t>
-  </si>
-  <si>
-    <t>/content/ConversionExperiments/outputs/docling_ablation/MANUAL DE MARKETING NASTIZOL MULTISINTOMAS/vlm_granite_docling_cuda/output.md</t>
-  </si>
-  <si>
-    <t>/content/ConversionExperiments/outputs/docling_ablation/MANUAL DE MARKETING NASTIZOL MULTISINTOMAS/standard_fast_no_ocr/output.json</t>
-  </si>
-  <si>
-    <t>/content/ConversionExperiments/outputs/docling_ablation/MANUAL DE MARKETING NASTIZOL MULTISINTOMAS/standard_accurate_no_ocr/output.json</t>
-  </si>
-  <si>
-    <t>/content/ConversionExperiments/outputs/docling_ablation/MANUAL DE MARKETING NASTIZOL MULTISINTOMAS/standard_accurate_cellmatch_false/output.json</t>
-  </si>
-  <si>
-    <t>/content/ConversionExperiments/outputs/docling_ablation/MANUAL DE MARKETING NASTIZOL MULTISINTOMAS/standard_tesseract_ocr_psm3/output.json</t>
-  </si>
-  <si>
-    <t>/content/ConversionExperiments/outputs/docling_ablation/MANUAL DE MARKETING NASTIZOL MULTISINTOMAS/standard_tesseract_force_ocr_psm6/output.json</t>
-  </si>
-  <si>
-    <t>/content/ConversionExperiments/outputs/docling_ablation/MANUAL DE MARKETING NASTIZOL MULTISINTOMAS/standard_easyocr_force_ocr/output.json</t>
-  </si>
-  <si>
-    <t>/content/ConversionExperiments/outputs/docling_ablation/MANUAL DE MARKETING NASTIZOL MULTISINTOMAS/standard_cuda_accurate/output.json</t>
-  </si>
-  <si>
-    <t>/content/ConversionExperiments/outputs/docling_ablation/MANUAL DE MARKETING NASTIZOL MULTISINTOMAS/vlm_granite_docling_cuda/output.json</t>
+    <t>/home/artrivas/ConversionExperiments/outputs/docling_ablation/MANUAL DE MARKETING NASTIZOL MULTISINTOMAS/standard_accurate_no_ocr/output.md</t>
+  </si>
+  <si>
+    <t>/home/artrivas/ConversionExperiments/outputs/docling_ablation/MANUAL DE MARKETING NASTIZOL MULTISINTOMAS/standard_accurate_no_ocr_doclingparse_cellmatch_true/output.md</t>
+  </si>
+  <si>
+    <t>/home/artrivas/ConversionExperiments/outputs/docling_ablation/MANUAL DE MARKETING NASTIZOL MULTISINTOMAS/standard_accurate_no_ocr_doclingparse_cellmatch_false/output.md</t>
+  </si>
+  <si>
+    <t>/home/artrivas/ConversionExperiments/outputs/docling_ablation/MANUAL DE MARKETING NASTIZOL MULTISINTOMAS/standard_accurate_no_ocr_pypdfium2_cellmatch_true/output.md</t>
+  </si>
+  <si>
+    <t>/home/artrivas/ConversionExperiments/outputs/docling_ablation/MANUAL DE MARKETING NASTIZOL MULTISINTOMAS/standard_accurate_no_ocr_pypdfium2_cellmatch_false/output.md</t>
+  </si>
+  <si>
+    <t>/home/artrivas/ConversionExperiments/outputs/docling_ablation/MANUAL DE MARKETING NASTIZOL MULTISINTOMAS/standard_accurate_no_ocr_threaded_doclingparse_cellmatch_true/output.md</t>
+  </si>
+  <si>
+    <t>/home/artrivas/ConversionExperiments/outputs/docling_ablation/MANUAL DE MARKETING NASTIZOL MULTISINTOMAS/standard_accurate_no_ocr_threaded_doclingparse_cellmatch_false/output.md</t>
+  </si>
+  <si>
+    <t>/home/artrivas/ConversionExperiments/outputs/docling_ablation/MANUAL DE MARKETING NASTIZOL MULTISINTOMAS/standard_accurate_no_ocr/output.json</t>
+  </si>
+  <si>
+    <t>/home/artrivas/ConversionExperiments/outputs/docling_ablation/MANUAL DE MARKETING NASTIZOL MULTISINTOMAS/standard_accurate_no_ocr_doclingparse_cellmatch_true/output.json</t>
+  </si>
+  <si>
+    <t>/home/artrivas/ConversionExperiments/outputs/docling_ablation/MANUAL DE MARKETING NASTIZOL MULTISINTOMAS/standard_accurate_no_ocr_doclingparse_cellmatch_false/output.json</t>
+  </si>
+  <si>
+    <t>/home/artrivas/ConversionExperiments/outputs/docling_ablation/MANUAL DE MARKETING NASTIZOL MULTISINTOMAS/standard_accurate_no_ocr_pypdfium2_cellmatch_true/output.json</t>
+  </si>
+  <si>
+    <t>/home/artrivas/ConversionExperiments/outputs/docling_ablation/MANUAL DE MARKETING NASTIZOL MULTISINTOMAS/standard_accurate_no_ocr_pypdfium2_cellmatch_false/output.json</t>
+  </si>
+  <si>
+    <t>/home/artrivas/ConversionExperiments/outputs/docling_ablation/MANUAL DE MARKETING NASTIZOL MULTISINTOMAS/standard_accurate_no_ocr_threaded_doclingparse_cellmatch_true/output.json</t>
+  </si>
+  <si>
+    <t>/home/artrivas/ConversionExperiments/outputs/docling_ablation/MANUAL DE MARKETING NASTIZOL MULTISINTOMAS/standard_accurate_no_ocr_threaded_doclingparse_cellmatch_false/output.json</t>
+  </si>
+  <si>
+    <t>/home/artrivas/ConversionExperiments/outputs/docling_ablation/MANUAL DE MARKETING NASTIZOL MULTISINTOMAS/standard_accurate_no_ocr</t>
+  </si>
+  <si>
+    <t>/home/artrivas/ConversionExperiments/outputs/docling_ablation/MANUAL DE MARKETING NASTIZOL MULTISINTOMAS/standard_accurate_no_ocr_doclingparse_cellmatch_true</t>
+  </si>
+  <si>
+    <t>/home/artrivas/ConversionExperiments/outputs/docling_ablation/MANUAL DE MARKETING NASTIZOL MULTISINTOMAS/standard_accurate_no_ocr_doclingparse_cellmatch_false</t>
+  </si>
+  <si>
+    <t>/home/artrivas/ConversionExperiments/outputs/docling_ablation/MANUAL DE MARKETING NASTIZOL MULTISINTOMAS/standard_accurate_no_ocr_pypdfium2_cellmatch_true</t>
+  </si>
+  <si>
+    <t>/home/artrivas/ConversionExperiments/outputs/docling_ablation/MANUAL DE MARKETING NASTIZOL MULTISINTOMAS/standard_accurate_no_ocr_pypdfium2_cellmatch_false</t>
+  </si>
+  <si>
+    <t>/home/artrivas/ConversionExperiments/outputs/docling_ablation/MANUAL DE MARKETING NASTIZOL MULTISINTOMAS/standard_accurate_no_ocr_threaded_doclingparse_cellmatch_true</t>
+  </si>
+  <si>
+    <t>/home/artrivas/ConversionExperiments/outputs/docling_ablation/MANUAL DE MARKETING NASTIZOL MULTISINTOMAS/standard_accurate_no_ocr_threaded_doclingparse_cellmatch_false</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -165,7 +256,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -173,30 +264,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -491,298 +564,626 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:AH8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+    <row r="1" spans="1:34">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>33</v>
+      </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:34">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2">
-        <v>32.93</v>
+        <v>42</v>
+      </c>
+      <c r="D2" t="s">
+        <v>43</v>
       </c>
       <c r="E2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H2">
+        <v>44</v>
+      </c>
+      <c r="F2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I2">
+        <v>140.129</v>
+      </c>
+      <c r="J2" t="s">
+        <v>46</v>
+      </c>
+      <c r="L2" t="s">
+        <v>50</v>
+      </c>
+      <c r="M2" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="b">
+        <v>0</v>
+      </c>
+      <c r="R2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <v>2</v>
+      </c>
+      <c r="U2" t="b">
+        <v>1</v>
+      </c>
+      <c r="V2" t="b">
+        <v>1</v>
+      </c>
+      <c r="W2" t="s">
+        <v>51</v>
+      </c>
+      <c r="X2" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD2">
+        <v>18</v>
+      </c>
+      <c r="AE2">
         <v>10</v>
       </c>
-      <c r="I2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J2" t="s">
-        <v>32</v>
+      <c r="AF2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>59</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>66</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:34">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3">
-        <v>18.278</v>
+        <v>42</v>
+      </c>
+      <c r="D3" t="s">
+        <v>43</v>
       </c>
       <c r="E3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H3">
+        <v>44</v>
+      </c>
+      <c r="F3" t="s">
+        <v>45</v>
+      </c>
+      <c r="I3">
+        <v>163.664</v>
+      </c>
+      <c r="J3" t="s">
+        <v>46</v>
+      </c>
+      <c r="K3" t="s">
+        <v>47</v>
+      </c>
+      <c r="L3" t="s">
+        <v>50</v>
+      </c>
+      <c r="M3" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="b">
+        <v>0</v>
+      </c>
+      <c r="R3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>2</v>
+      </c>
+      <c r="U3" t="b">
+        <v>1</v>
+      </c>
+      <c r="V3" t="b">
+        <v>1</v>
+      </c>
+      <c r="W3" t="s">
+        <v>51</v>
+      </c>
+      <c r="X3" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD3">
+        <v>18</v>
+      </c>
+      <c r="AE3">
         <v>10</v>
       </c>
-      <c r="I3" t="s">
-        <v>25</v>
-      </c>
-      <c r="J3" t="s">
-        <v>33</v>
+      <c r="AF3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>60</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>67</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:34">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4">
-        <v>19.138</v>
+        <v>42</v>
+      </c>
+      <c r="D4" t="s">
+        <v>43</v>
       </c>
       <c r="E4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G4" t="s">
-        <v>23</v>
-      </c>
-      <c r="H4">
+        <v>44</v>
+      </c>
+      <c r="F4" t="s">
+        <v>45</v>
+      </c>
+      <c r="I4">
+        <v>144.234</v>
+      </c>
+      <c r="J4" t="s">
+        <v>46</v>
+      </c>
+      <c r="K4" t="s">
+        <v>47</v>
+      </c>
+      <c r="L4" t="s">
+        <v>50</v>
+      </c>
+      <c r="M4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="b">
+        <v>0</v>
+      </c>
+      <c r="R4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>2</v>
+      </c>
+      <c r="U4" t="b">
+        <v>1</v>
+      </c>
+      <c r="V4" t="b">
+        <v>1</v>
+      </c>
+      <c r="W4" t="s">
+        <v>51</v>
+      </c>
+      <c r="X4" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD4">
+        <v>18</v>
+      </c>
+      <c r="AE4">
         <v>10</v>
       </c>
-      <c r="I4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J4" t="s">
+      <c r="AF4" t="s">
+        <v>54</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>61</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="5" spans="1:34">
+      <c r="A5" t="s">
         <v>34</v>
       </c>
+      <c r="B5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E5" t="s">
+        <v>44</v>
+      </c>
+      <c r="F5" t="s">
+        <v>45</v>
+      </c>
+      <c r="I5">
+        <v>156.764</v>
+      </c>
+      <c r="J5" t="s">
+        <v>46</v>
+      </c>
+      <c r="K5" t="s">
+        <v>48</v>
+      </c>
+      <c r="L5" t="s">
+        <v>50</v>
+      </c>
+      <c r="M5" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="b">
+        <v>0</v>
+      </c>
+      <c r="R5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>2</v>
+      </c>
+      <c r="U5" t="b">
+        <v>1</v>
+      </c>
+      <c r="V5" t="b">
+        <v>1</v>
+      </c>
+      <c r="W5" t="s">
+        <v>51</v>
+      </c>
+      <c r="X5" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD5">
+        <v>18</v>
+      </c>
+      <c r="AE5">
+        <v>10</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>55</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>62</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>69</v>
+      </c>
     </row>
-    <row r="5" spans="1:11">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5">
-        <v>30.915</v>
-      </c>
-      <c r="E5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H5">
+    <row r="6" spans="1:34">
+      <c r="A6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E6" t="s">
+        <v>44</v>
+      </c>
+      <c r="F6" t="s">
+        <v>45</v>
+      </c>
+      <c r="I6">
+        <v>162.423</v>
+      </c>
+      <c r="J6" t="s">
+        <v>46</v>
+      </c>
+      <c r="K6" t="s">
+        <v>48</v>
+      </c>
+      <c r="L6" t="s">
+        <v>50</v>
+      </c>
+      <c r="M6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="b">
+        <v>0</v>
+      </c>
+      <c r="R6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>2</v>
+      </c>
+      <c r="U6" t="b">
+        <v>1</v>
+      </c>
+      <c r="V6" t="b">
+        <v>1</v>
+      </c>
+      <c r="W6" t="s">
+        <v>51</v>
+      </c>
+      <c r="X6" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD6">
+        <v>18</v>
+      </c>
+      <c r="AE6">
         <v>10</v>
       </c>
-      <c r="I5" t="s">
-        <v>27</v>
-      </c>
-      <c r="J5" t="s">
-        <v>35</v>
+      <c r="AF6" t="s">
+        <v>56</v>
+      </c>
+      <c r="AG6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>70</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
-      <c r="A6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6">
-        <v>36.591</v>
-      </c>
-      <c r="E6" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6" t="b">
-        <v>1</v>
-      </c>
-      <c r="G6" t="s">
-        <v>23</v>
-      </c>
-      <c r="H6">
-        <v>10</v>
-      </c>
-      <c r="I6" t="s">
-        <v>28</v>
-      </c>
-      <c r="J6" t="s">
-        <v>36</v>
+    <row r="7" spans="1:34">
+      <c r="A7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E7" t="s">
+        <v>44</v>
+      </c>
+      <c r="F7" t="s">
+        <v>45</v>
+      </c>
+      <c r="I7">
+        <v>60.174</v>
+      </c>
+      <c r="J7" t="s">
+        <v>46</v>
+      </c>
+      <c r="K7" t="s">
+        <v>49</v>
+      </c>
+      <c r="L7" t="s">
+        <v>50</v>
+      </c>
+      <c r="M7" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="b">
+        <v>0</v>
+      </c>
+      <c r="R7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>2</v>
+      </c>
+      <c r="U7" t="b">
+        <v>1</v>
+      </c>
+      <c r="V7" t="b">
+        <v>1</v>
+      </c>
+      <c r="W7" t="s">
+        <v>51</v>
+      </c>
+      <c r="X7" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD7">
+        <v>18</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="s">
+        <v>57</v>
+      </c>
+      <c r="AG7" t="s">
+        <v>64</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>71</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
-      <c r="A7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" t="s">
-        <v>20</v>
-      </c>
-      <c r="D7">
-        <v>32.067</v>
-      </c>
-      <c r="E7" t="s">
-        <v>21</v>
-      </c>
-      <c r="F7" t="b">
-        <v>1</v>
-      </c>
-      <c r="G7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H7">
-        <v>10</v>
-      </c>
-      <c r="I7" t="s">
-        <v>29</v>
-      </c>
-      <c r="J7" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:34">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="B8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" t="s">
+        <v>44</v>
+      </c>
+      <c r="F8" t="s">
+        <v>45</v>
+      </c>
+      <c r="I8">
+        <v>58.131</v>
+      </c>
+      <c r="J8" t="s">
+        <v>46</v>
+      </c>
+      <c r="K8" t="s">
+        <v>49</v>
+      </c>
+      <c r="L8" t="s">
+        <v>50</v>
+      </c>
+      <c r="M8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="b">
+        <v>0</v>
+      </c>
+      <c r="R8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>2</v>
+      </c>
+      <c r="U8" t="b">
+        <v>1</v>
+      </c>
+      <c r="V8" t="b">
+        <v>1</v>
+      </c>
+      <c r="W8" t="s">
+        <v>51</v>
+      </c>
+      <c r="X8" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD8">
         <v>18</v>
       </c>
-      <c r="C8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8">
-        <v>29.889</v>
-      </c>
-      <c r="E8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F8" t="b">
-        <v>1</v>
-      </c>
-      <c r="G8" t="s">
-        <v>23</v>
-      </c>
-      <c r="H8">
-        <v>10</v>
-      </c>
-      <c r="I8" t="s">
-        <v>30</v>
-      </c>
-      <c r="J8" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
-      <c r="A9" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" t="s">
-        <v>20</v>
-      </c>
-      <c r="D9">
-        <v>852.516</v>
-      </c>
-      <c r="E9" t="s">
-        <v>22</v>
-      </c>
-      <c r="F9" t="b">
-        <v>1</v>
-      </c>
-      <c r="G9" t="s">
-        <v>23</v>
-      </c>
-      <c r="H9">
-        <v>6</v>
-      </c>
-      <c r="I9" t="s">
-        <v>31</v>
-      </c>
-      <c r="J9" t="s">
-        <v>39</v>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="s">
+        <v>58</v>
+      </c>
+      <c r="AG8" t="s">
+        <v>65</v>
+      </c>
+      <c r="AH8" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
